--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$66</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4148" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2546" uniqueCount="392">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -616,127 +616,6 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Condition.clinicalStatus.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.clinicalStatus.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.clinicalStatus.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Condition.clinicalStatus.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Condition.clinicalStatus.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Condition.clinicalStatus.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Condition.clinicalStatus.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
     <t>Condition.clinicalStatus.text</t>
   </si>
   <si>
@@ -804,27 +683,6 @@
   </si>
   <si>
     <t>Condition.verificationStatus.coding</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.system</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.version</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.code</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.display</t>
-  </si>
-  <si>
-    <t>Condition.verificationStatus.coding.userSelected</t>
   </si>
   <si>
     <t>Condition.verificationStatus.text</t>
@@ -990,27 +848,6 @@
     <t>Condition.bodySite.coding</t>
   </si>
   <si>
-    <t>Condition.bodySite.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.system</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.version</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.code</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.display</t>
-  </si>
-  <si>
-    <t>Condition.bodySite.coding.userSelected</t>
-  </si>
-  <si>
     <t>Condition.bodySite.text</t>
   </si>
   <si>
@@ -1257,27 +1094,6 @@
     <t>Condition.stage.summary.coding</t>
   </si>
   <si>
-    <t>Condition.stage.summary.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.stage.summary.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.stage.summary.coding.system</t>
-  </si>
-  <si>
-    <t>Condition.stage.summary.coding.version</t>
-  </si>
-  <si>
-    <t>Condition.stage.summary.coding.code</t>
-  </si>
-  <si>
-    <t>Condition.stage.summary.coding.display</t>
-  </si>
-  <si>
-    <t>Condition.stage.summary.coding.userSelected</t>
-  </si>
-  <si>
     <t>Condition.stage.summary.text</t>
   </si>
   <si>
@@ -1324,27 +1140,6 @@
     <t>Condition.stage.type.coding</t>
   </si>
   <si>
-    <t>Condition.stage.type.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.stage.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.stage.type.coding.system</t>
-  </si>
-  <si>
-    <t>Condition.stage.type.coding.version</t>
-  </si>
-  <si>
-    <t>Condition.stage.type.coding.code</t>
-  </si>
-  <si>
-    <t>Condition.stage.type.coding.display</t>
-  </si>
-  <si>
-    <t>Condition.stage.type.coding.userSelected</t>
-  </si>
-  <si>
     <t>Condition.stage.type.text</t>
   </si>
   <si>
@@ -1411,27 +1206,6 @@
   </si>
   <si>
     <t>Condition.evidence.code.coding</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.id</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.system</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.version</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.code</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.display</t>
-  </si>
-  <si>
-    <t>Condition.evidence.code.coding.userSelected</t>
   </si>
   <si>
     <t>Condition.evidence.code.text</t>
@@ -1786,11 +1560,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP108"/>
+  <dimension ref="A1:AP66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.20703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.20703125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.90234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.90234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3640,7 +3414,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>192</v>
       </c>
@@ -3659,25 +3433,29 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>172</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>79</v>
       </c>
@@ -3725,7 +3503,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3737,7 +3515,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>79</v>
@@ -3746,10 +3524,10 @@
         <v>79</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>79</v>
@@ -3758,44 +3536,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3821,69 +3599,69 @@
         <v>79</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>79</v>
+        <v>206</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>79</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3903,23 +3681,19 @@
         <v>79</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>79</v>
       </c>
@@ -3967,7 +3741,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3979,7 +3753,7 @@
         <v>79</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>79</v>
@@ -3988,10 +3762,10 @@
         <v>79</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -4002,21 +3776,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>79</v>
@@ -4025,19 +3799,19 @@
         <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4075,31 +3849,31 @@
         <v>79</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>79</v>
@@ -4108,10 +3882,10 @@
         <v>79</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4122,10 +3896,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4136,7 +3910,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>92</v>
@@ -4148,17 +3922,19 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>79</v>
@@ -4207,13 +3983,13 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>79</v>
@@ -4228,24 +4004,24 @@
         <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>216</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4259,7 +4035,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>79</v>
@@ -4271,14 +4047,16 @@
         <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O21" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4327,7 +4105,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4348,10 +4126,10 @@
         <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4360,12 +4138,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4376,32 +4154,30 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>158</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
       </c>
@@ -4425,13 +4201,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>79</v>
+        <v>217</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>79</v>
+        <v>220</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4449,13 +4225,13 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>79</v>
@@ -4467,27 +4243,27 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>79</v>
+        <v>224</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4501,29 +4277,27 @@
         <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>79</v>
       </c>
@@ -4547,13 +4321,13 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>79</v>
+        <v>227</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>79</v>
+        <v>229</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
@@ -4571,7 +4345,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4589,31 +4363,31 @@
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>79</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>79</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>79</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4626,7 +4400,7 @@
         <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>92</v>
@@ -4635,15 +4409,15 @@
         <v>158</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4667,13 +4441,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4691,7 +4465,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4700,36 +4474,36 @@
         <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>246</v>
+        <v>79</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4844,10 +4618,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4964,10 +4738,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5084,12 +4858,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5103,25 +4877,29 @@
         <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>172</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
@@ -5169,7 +4947,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5181,7 +4959,7 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5190,10 +4968,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5202,16 +4980,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5221,25 +4999,25 @@
         <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>140</v>
+        <v>256</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5265,31 +5043,31 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>79</v>
+        <v>257</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>79</v>
+        <v>258</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>182</v>
+        <v>253</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5301,33 +5079,33 @@
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>79</v>
+        <v>259</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>176</v>
+        <v>260</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>79</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5347,23 +5125,19 @@
         <v>79</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5411,7 +5185,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5423,7 +5197,7 @@
         <v>79</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>79</v>
@@ -5432,10 +5206,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5446,21 +5220,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
@@ -5469,19 +5243,19 @@
         <v>79</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>203</v>
+        <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>205</v>
+        <v>140</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5519,31 +5293,31 @@
         <v>79</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5552,10 +5326,10 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5566,10 +5340,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5580,7 +5354,7 @@
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>92</v>
@@ -5592,17 +5366,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5651,13 +5427,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -5672,10 +5448,10 @@
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5684,12 +5460,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5703,7 +5479,7 @@
         <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>79</v>
@@ -5715,14 +5491,16 @@
         <v>172</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5771,7 +5549,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5792,10 +5570,10 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5804,26 +5582,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>267</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
@@ -5832,19 +5610,17 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>227</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -5893,10 +5669,10 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>91</v>
@@ -5908,30 +5684,30 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>272</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>230</v>
+        <v>273</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5945,7 +5721,7 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -5954,20 +5730,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>172</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
       </c>
@@ -6015,7 +5789,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6030,30 +5804,30 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6064,28 +5838,28 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K36" t="s" s="2">
-        <v>158</v>
+        <v>286</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6111,13 +5885,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>266</v>
+        <v>79</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6135,13 +5909,13 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>79</v>
@@ -6150,30 +5924,30 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>290</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6187,7 +5961,7 @@
         <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>79</v>
@@ -6196,16 +5970,16 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>158</v>
+        <v>286</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6231,13 +6005,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>274</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>276</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6255,7 +6029,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6264,7 +6038,7 @@
         <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>103</v>
@@ -6273,31 +6047,31 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6307,7 +6081,7 @@
         <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>79</v>
@@ -6316,18 +6090,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>158</v>
+        <v>302</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>286</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6351,13 +6123,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6375,7 +6147,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6390,30 +6162,30 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>291</v>
+        <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>295</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6433,16 +6205,16 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>173</v>
+        <v>310</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>174</v>
+        <v>311</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6493,7 +6265,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6505,7 +6277,7 @@
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>79</v>
@@ -6517,10 +6289,10 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>176</v>
+        <v>312</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6528,21 +6300,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6551,20 +6323,18 @@
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>309</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>138</v>
+        <v>315</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
@@ -6601,31 +6371,31 @@
         <v>79</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>182</v>
+        <v>314</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>79</v>
@@ -6634,24 +6404,24 @@
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>176</v>
+        <v>318</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6665,29 +6435,25 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>185</v>
+        <v>322</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
       </c>
@@ -6735,7 +6501,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6747,7 +6513,7 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>103</v>
+        <v>324</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
@@ -6756,10 +6522,10 @@
         <v>79</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6768,12 +6534,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6787,29 +6553,25 @@
         <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>172</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>233</v>
+        <v>173</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6857,7 +6619,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6869,7 +6631,7 @@
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -6878,10 +6640,10 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -6890,16 +6652,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6909,25 +6671,25 @@
         <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>301</v>
+        <v>138</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
+        <v>178</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6953,13 +6715,13 @@
         <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6977,7 +6739,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>300</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6989,65 +6751,69 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>307</v>
+        <v>176</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>308</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>173</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7095,19 +6861,19 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>175</v>
+        <v>332</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>79</v>
@@ -7119,7 +6885,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7128,26 +6894,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7156,17 +6922,15 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7191,55 +6955,55 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>79</v>
+        <v>168</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7248,12 +7012,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7264,32 +7028,28 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7337,19 +7097,19 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7358,10 +7118,10 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7372,21 +7132,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7398,15 +7158,17 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7443,31 +7205,31 @@
         <v>79</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7488,16 +7250,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7507,27 +7269,29 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7563,19 +7327,19 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>181</v>
+        <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7587,7 +7351,7 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7596,10 +7360,10 @@
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7608,12 +7372,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7627,7 +7391,7 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
@@ -7636,19 +7400,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>79</v>
@@ -7697,7 +7461,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7718,10 +7482,10 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7732,10 +7496,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7746,7 +7510,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7755,20 +7519,18 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>172</v>
+        <v>345</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>203</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7817,16 +7579,16 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>103</v>
@@ -7838,10 +7600,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>208</v>
+        <v>348</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7852,10 +7614,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>316</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7875,21 +7637,19 @@
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>210</v>
+        <v>350</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>211</v>
+        <v>351</v>
       </c>
       <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -7913,13 +7673,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>79</v>
+        <v>352</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7937,7 +7697,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>213</v>
+        <v>349</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7958,10 +7718,10 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>215</v>
+        <v>354</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7972,10 +7732,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7995,21 +7755,19 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>172</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>217</v>
+        <v>173</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>218</v>
+        <v>174</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8057,7 +7815,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8069,7 +7827,7 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8078,10 +7836,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8092,21 +7850,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8115,23 +7873,21 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8167,31 +7923,31 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8200,10 +7956,10 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8212,12 +7968,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8228,10 +7984,10 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
@@ -8240,19 +7996,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>236</v>
+        <v>188</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8301,13 +8057,13 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>237</v>
+        <v>189</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>79</v>
@@ -8322,10 +8078,10 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8336,18 +8092,18 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>321</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>91</v>
@@ -8362,17 +8118,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>322</v>
+        <v>172</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>325</v>
+        <v>196</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8421,10 +8179,10 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>320</v>
+        <v>197</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>91</v>
@@ -8436,30 +8194,30 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>327</v>
+        <v>198</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>328</v>
+        <v>199</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>329</v>
+        <v>79</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8470,28 +8228,28 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8541,34 +8299,34 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>103</v>
+        <v>363</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>338</v>
+        <v>79</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8576,10 +8334,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8599,20 +8357,18 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>340</v>
+        <v>172</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>341</v>
+        <v>173</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8661,7 +8417,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>339</v>
+        <v>175</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8673,22 +8429,22 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>344</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>345</v>
+        <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>346</v>
+        <v>176</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>347</v>
+        <v>79</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8696,21 +8452,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8722,16 +8478,16 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>340</v>
+        <v>137</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>349</v>
+        <v>138</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>350</v>
+        <v>178</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>351</v>
+        <v>140</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8781,19 +8537,19 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>348</v>
+        <v>182</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>352</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -8805,10 +8561,10 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>353</v>
+        <v>176</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>79</v>
@@ -8816,42 +8572,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>356</v>
+        <v>137</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8899,19 +8659,19 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
@@ -8920,24 +8680,24 @@
         <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>359</v>
+        <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>360</v>
+        <v>134</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8948,10 +8708,10 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>79</v>
@@ -8960,13 +8720,13 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>363</v>
+        <v>158</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8993,13 +8753,13 @@
         <v>79</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>79</v>
@@ -9017,34 +8777,34 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>221</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>79</v>
@@ -9052,10 +8812,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9075,16 +8835,16 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>363</v>
+        <v>172</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>369</v>
+        <v>173</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>370</v>
+        <v>174</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9135,7 +8895,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>368</v>
+        <v>175</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9147,7 +8907,7 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9156,13 +8916,13 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>372</v>
+        <v>176</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>79</v>
@@ -9170,14 +8930,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9196,15 +8956,17 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>375</v>
+        <v>137</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>376</v>
+        <v>138</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9241,19 +9003,19 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>374</v>
+        <v>182</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9265,7 +9027,7 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>378</v>
+        <v>142</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
@@ -9277,21 +9039,21 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>380</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9302,28 +9064,32 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9371,19 +9137,19 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
@@ -9392,10 +9158,10 @@
         <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9404,46 +9170,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9491,19 +9259,19 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
@@ -9512,10 +9280,10 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>79</v>
+        <v>198</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9526,14 +9294,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9546,26 +9314,22 @@
         <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>137</v>
+        <v>382</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
       </c>
@@ -9613,7 +9377,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9622,10 +9386,10 @@
         <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -9637,10 +9401,10 @@
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>134</v>
+        <v>348</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>79</v>
@@ -9648,10 +9412,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9662,7 +9426,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>92</v>
@@ -9674,13 +9438,13 @@
         <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>158</v>
+        <v>386</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9707,13 +9471,13 @@
         <v>79</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>287</v>
+        <v>79</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -9731,5083 +9495,41 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>79</v>
+        <v>389</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>393</v>
+        <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>168</v>
+        <v>390</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>293</v>
+        <v>391</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O68" s="2"/>
-      <c r="P68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="P82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP108" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP108">
+  <autoFilter ref="A1:AP66">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14817,7 +9539,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI107">
+  <conditionalFormatting sqref="A2:AI65">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-condition.xlsx
+++ b/dev/StructureDefinition-ph-core-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
